--- a/material/INVENTARIO DE LIBROS.xlsx
+++ b/material/INVENTARIO DE LIBROS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Documents\Biblioteca Roncedo\material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45F71B34-C17E-45C3-B957-C3E37CD7B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{FED5C9F3-A10A-418E-ABD2-AECC1639DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
